--- a/Compititor's_Price/IKO_Prices/IKO_Prices_23-10-2025.xlsx
+++ b/Compititor's_Price/IKO_Prices/IKO_Prices_23-10-2025.xlsx
@@ -498,27 +498,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>£10.45</t>
+          <t>£10.40</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>£10.45</t>
+          <t>£10.40</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>£10.45</t>
+          <t>£10.40</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -555,27 +555,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>£11.86</t>
+          <t>£11.81</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>£11.86</t>
+          <t>£11.81</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>£11.86</t>
+          <t>£11.81</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
     </row>
@@ -627,12 +627,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -652,7 +652,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
     </row>
@@ -669,27 +669,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>£15.56</t>
+          <t>£15.47</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>£15.56</t>
+          <t>£15.47</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>£15.56</t>
+          <t>£15.47</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
     </row>
@@ -726,27 +726,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£19.79</t>
+          <t>£19.69</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>£19.79</t>
+          <t>£19.69</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>£19.79</t>
+          <t>£19.69</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
     </row>
@@ -798,12 +798,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
     </row>
@@ -855,12 +855,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -912,12 +912,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
     </row>
@@ -1011,27 +1011,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£26.74</t>
+          <t>£26.51</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£26.74</t>
+          <t>£26.51</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£26.74</t>
+          <t>£26.51</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
     </row>
@@ -1068,17 +1068,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>£35.04</t>
+          <t>£34.65</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>£35.04</t>
+          <t>£34.65</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>£35.04</t>
+          <t>£34.65</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
     </row>
@@ -1125,27 +1125,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>£32.74</t>
+          <t>£32.55</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>£32.74</t>
+          <t>£32.55</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>£32.74</t>
+          <t>£32.55</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
     </row>
@@ -1182,27 +1182,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>£40.66</t>
+          <t>£40.22</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>£40.66</t>
+          <t>£40.22</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>£40.66</t>
+          <t>£40.22</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
     </row>
@@ -1239,27 +1239,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>£40.11</t>
+          <t>£39.90</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>£40.11</t>
+          <t>£39.90</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>£40.11</t>
+          <t>£39.90</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>POA</t>
         </is>
       </c>
     </row>
